--- a/docs/downloads/05/tbl_cooking_alaotra_tous.xlsx
+++ b/docs/downloads/05/tbl_cooking_alaotra_tous.xlsx
@@ -405,12 +405,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -567,12 +561,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -639,12 +627,6 @@
           <t>Gaz</t>
         </is>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>0.9</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -711,12 +693,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C20">
-        <v>2</v>
-      </c>
-      <c r="D20">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -746,12 +722,6 @@
         <is>
           <t>Gaz</t>
         </is>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>0.2</v>
       </c>
     </row>
     <row r="23">

--- a/docs/downloads/05/tbl_cooking_alaotra_tous.xlsx
+++ b/docs/downloads/05/tbl_cooking_alaotra_tous.xlsx
@@ -384,7 +384,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C2">
@@ -421,7 +421,7 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>43.7</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="5">
@@ -432,14 +432,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C5">
         <v>48</v>
       </c>
       <c r="D5">
-        <v>55.2</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -457,7 +457,7 @@
         <v>17</v>
       </c>
       <c r="D6">
-        <v>24.6</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="7">
@@ -468,14 +468,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C7">
         <v>52</v>
       </c>
       <c r="D7">
-        <v>75.40000000000001</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>36</v>
       </c>
       <c r="D8">
-        <v>51.4</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="9">
@@ -504,14 +504,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C9">
         <v>34</v>
       </c>
       <c r="D9">
-        <v>48.6</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -529,7 +529,7 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>17.6</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="11">
@@ -540,14 +540,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C11">
         <v>42</v>
       </c>
       <c r="D11">
-        <v>82.40000000000001</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="12">
@@ -577,7 +577,7 @@
         <v>49</v>
       </c>
       <c r="D13">
-        <v>40.5</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="14">
@@ -588,14 +588,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C14">
         <v>71</v>
       </c>
       <c r="D14">
-        <v>58.7</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -613,7 +613,7 @@
         <v>44</v>
       </c>
       <c r="D15">
-        <v>37.6</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="16">
@@ -636,14 +636,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C17">
         <v>72</v>
       </c>
       <c r="D17">
-        <v>61.5</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -661,7 +661,7 @@
         <v>25</v>
       </c>
       <c r="D18">
-        <v>26.3</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="19">
@@ -672,14 +672,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C19">
         <v>70</v>
       </c>
       <c r="D19">
-        <v>73.7</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -709,7 +709,7 @@
         <v>218</v>
       </c>
       <c r="D21">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22">
@@ -732,14 +732,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C23">
         <v>420</v>
       </c>
       <c r="D23">
-        <v>65.5</v>
+        <v>82.8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/05/tbl_cooking_alaotra_tous.xlsx
+++ b/docs/downloads/05/tbl_cooking_alaotra_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -397,7 +397,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -409,7 +409,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -427,7 +427,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -445,7 +445,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -463,7 +463,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -517,7 +517,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -601,7 +601,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -649,7 +649,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -685,7 +685,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -697,7 +697,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
